--- a/data/trans_camb/P6903-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P6903-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-23,51; 6,68</t>
+          <t>-25,91; 4,08</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,13; 35,04</t>
+          <t>1,11; 35,05</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-11,23; 29,14</t>
+          <t>-11,16; 27,77</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-27,92; 13,84</t>
+          <t>-29,13; 13,88</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-24,21; 32,33</t>
+          <t>-19,11; 33,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-9,57; 46,23</t>
+          <t>-6,7; 47,6</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-20,62; 3,97</t>
+          <t>-20,86; 3,82</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,42; 31,28</t>
+          <t>1,89; 29,77</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 33,44</t>
+          <t>-3,3; 31,0</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-60,45; 23,98</t>
+          <t>-64,82; 15,44</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,91; 122,2</t>
+          <t>4,11; 120,42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-29,82; 98,4</t>
+          <t>-29,1; 98,64</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-59,35; 58,45</t>
+          <t>-62,45; 53,04</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-51,98; 115,89</t>
+          <t>-44,75; 120,86</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-23,83; 185,69</t>
+          <t>-17,99; 203,04</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-51,9; 13,67</t>
+          <t>-53,06; 13,82</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,35; 107,24</t>
+          <t>5,23; 96,3</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-8,49; 114,46</t>
+          <t>-8,61; 100,43</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-13,99; 2,48</t>
+          <t>-14,84; 2,24</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 14,75</t>
+          <t>-3,06; 14,83</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,74; 11,26</t>
+          <t>-7,67; 10,33</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,34; 16,85</t>
+          <t>-6,64; 17,32</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 21,98</t>
+          <t>-2,94; 22,8</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-15,29; 14,04</t>
+          <t>-13,73; 13,48</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-9,42; 4,32</t>
+          <t>-8,47; 5,51</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,4; 14,35</t>
+          <t>1,47; 14,84</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-5,84; 8,9</t>
+          <t>-6,63; 8,98</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-40,99; 9,62</t>
+          <t>-42,3; 9,09</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,51; 55,42</t>
+          <t>-8,56; 56,67</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-19,31; 41,55</t>
+          <t>-21,5; 37,37</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-20,52; 61,23</t>
+          <t>-17,1; 68,6</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-5,6; 83,54</t>
+          <t>-7,94; 86,38</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-37,76; 50,37</t>
+          <t>-35,54; 50,29</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-26,81; 15,43</t>
+          <t>-24,56; 19,74</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,59; 50,44</t>
+          <t>4,67; 53,98</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-17,13; 31,31</t>
+          <t>-19,14; 30,98</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-25,89; 7,78</t>
+          <t>-24,69; 6,8</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-16,29; 17,14</t>
+          <t>-15,15; 17,74</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-9,02; 25,19</t>
+          <t>-8,19; 24,99</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-10,99; 24,97</t>
+          <t>-9,64; 25,17</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 31,24</t>
+          <t>-2,28; 30,24</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,77; 35,43</t>
+          <t>7,34; 35,84</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-14,75; 10,42</t>
+          <t>-14,51; 10,12</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,07; 18,94</t>
+          <t>-2,2; 19,73</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,17; 25,99</t>
+          <t>3,85; 25,46</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-70,52; 37,2</t>
+          <t>-68,63; 31,8</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-45,73; 75,5</t>
+          <t>-41,62; 84,99</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-26,41; 116,26</t>
+          <t>-24,07; 116,92</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-39,2; 166,68</t>
+          <t>-34,55; 155,86</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 203,23</t>
+          <t>-8,58; 177,2</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>20,03; 238,99</t>
+          <t>19,51; 244,7</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-46,01; 46,86</t>
+          <t>-46,89; 45,67</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-13,16; 85,64</t>
+          <t>-6,99; 92,63</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>9,77; 124,03</t>
+          <t>10,42; 117,5</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-14,31; -1,61</t>
+          <t>-14,06; -1,14</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 13,86</t>
+          <t>-0,67; 14,34</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,23; 9,92</t>
+          <t>-4,77; 10,54</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,4; 12,8</t>
+          <t>-5,52; 13,35</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,1; 19,88</t>
+          <t>1,41; 20,43</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,41; 16,17</t>
+          <t>-4,23; 17,06</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-8,15; 2,58</t>
+          <t>-8,03; 3,01</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,7; 14,19</t>
+          <t>2,7; 14,28</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 10,63</t>
+          <t>-1,59; 11,47</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-40,66; -5,89</t>
+          <t>-40,83; -3,87</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 47,2</t>
+          <t>-1,8; 50,43</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-12,49; 33,81</t>
+          <t>-14,21; 36,19</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-15,47; 48,02</t>
+          <t>-15,07; 52,06</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>6,26; 78,9</t>
+          <t>4,13; 78,2</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-11,71; 60,97</t>
+          <t>-10,85; 64,7</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-24,25; 9,18</t>
+          <t>-23,88; 8,91</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>8,2; 48,66</t>
+          <t>7,82; 48,99</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 36,21</t>
+          <t>-3,67; 40,85</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P6903-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P6903-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8,16</t>
+          <t>10,16</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,94</t>
+          <t>3,82</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>12,46</t>
+          <t>8,12</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-25,91; 4,08</t>
+          <t>-22,64; 5,74</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,11; 35,05</t>
+          <t>2,49; 36,37</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-11,16; 27,77</t>
+          <t>-8,23; 29,86</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-29,13; 13,88</t>
+          <t>-30,13; 14,96</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-19,11; 33,0</t>
+          <t>-21,67; 32,26</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-6,7; 47,6</t>
+          <t>-18,19; 26,28</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-20,86; 3,82</t>
+          <t>-21,21; 3,84</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,89; 29,77</t>
+          <t>1,48; 30,66</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 31,0</t>
+          <t>-6,15; 22,83</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>42,13%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>35,29%</t>
+          <t>23,0%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-64,82; 15,44</t>
+          <t>-59,0; 24,73</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,11; 120,42</t>
+          <t>6,92; 132,3</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-29,1; 98,64</t>
+          <t>-22,85; 104,82</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-62,45; 53,04</t>
+          <t>-62,36; 62,47</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-44,75; 120,86</t>
+          <t>-48,47; 119,09</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-17,99; 203,04</t>
+          <t>-38,15; 96,83</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-53,06; 13,82</t>
+          <t>-52,25; 14,02</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,23; 96,3</t>
+          <t>2,85; 100,6</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-8,61; 100,43</t>
+          <t>-15,8; 77,6</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,66</t>
+          <t>3,02</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,91</t>
+          <t>9,14</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2,57</t>
+          <t>6,02</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-14,84; 2,24</t>
+          <t>-15,07; 1,79</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 14,83</t>
+          <t>-3,01; 14,83</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,67; 10,33</t>
+          <t>-6,46; 11,55</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,64; 17,32</t>
+          <t>-6,71; 17,6</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 22,8</t>
+          <t>-0,88; 22,75</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-13,73; 13,48</t>
+          <t>-0,69; 19,92</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-8,47; 5,51</t>
+          <t>-8,26; 4,99</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,47; 14,84</t>
+          <t>0,41; 15,1</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-6,63; 8,98</t>
+          <t>-0,92; 11,97</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>19,15%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-42,3; 9,09</t>
+          <t>-43,33; 8,55</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-8,56; 56,67</t>
+          <t>-7,87; 56,58</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-21,5; 37,37</t>
+          <t>-18,52; 42,58</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-17,1; 68,6</t>
+          <t>-16,48; 68,39</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-7,94; 86,38</t>
+          <t>-2,45; 88,33</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-35,54; 50,29</t>
+          <t>-2,23; 82,8</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-24,56; 19,74</t>
+          <t>-25,12; 18,06</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,67; 53,98</t>
+          <t>1,13; 54,66</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-19,14; 30,98</t>
+          <t>-1,46; 42,79</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6,87</t>
+          <t>9,94</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>21,5</t>
+          <t>22,03</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>14,52</t>
+          <t>16,13</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-24,69; 6,8</t>
+          <t>-24,33; 9,45</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-15,15; 17,74</t>
+          <t>-13,78; 17,15</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-8,19; 24,99</t>
+          <t>-7,0; 26,15</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,64; 25,17</t>
+          <t>-11,2; 23,16</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 30,24</t>
+          <t>-0,07; 31,43</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,34; 35,84</t>
+          <t>5,93; 34,74</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-14,51; 10,12</t>
+          <t>-13,37; 11,98</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 19,73</t>
+          <t>-4,07; 19,32</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,85; 25,46</t>
+          <t>5,3; 27,42</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>33,56%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,81%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>54,08%</t>
+          <t>60,07%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-68,63; 31,8</t>
+          <t>-69,1; 40,55</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-41,62; 84,99</t>
+          <t>-39,25; 78,97</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-24,07; 116,92</t>
+          <t>-21,42; 116,36</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-34,55; 155,86</t>
+          <t>-40,08; 145,82</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-8,58; 177,2</t>
+          <t>-2,15; 194,77</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19,51; 244,7</t>
+          <t>17,24; 239,99</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-46,89; 45,67</t>
+          <t>-42,91; 53,71</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-6,99; 92,63</t>
+          <t>-11,45; 93,51</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>10,42; 117,5</t>
+          <t>15,55; 135,99</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2,72</t>
+          <t>4,56</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,33</t>
+          <t>11,95</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>5,44</t>
+          <t>7,94</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-14,06; -1,14</t>
+          <t>-13,93; -0,6</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 14,34</t>
+          <t>-0,15; 14,16</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,77; 10,54</t>
+          <t>-2,49; 11,78</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,52; 13,35</t>
+          <t>-5,18; 13,04</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,41; 20,43</t>
+          <t>2,29; 20,53</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,23; 17,06</t>
+          <t>3,44; 18,9</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-8,03; 3,01</t>
+          <t>-8,11; 2,87</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,7; 14,28</t>
+          <t>2,58; 14,14</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 11,47</t>
+          <t>3,2; 13,33</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>38,83%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>25,35%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-40,83; -3,87</t>
+          <t>-40,69; -2,24</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 50,43</t>
+          <t>-1,1; 49,38</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-14,21; 36,19</t>
+          <t>-7,6; 40,65</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-15,07; 52,06</t>
+          <t>-14,61; 51,28</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,13; 78,2</t>
+          <t>5,88; 78,05</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-10,85; 64,7</t>
+          <t>9,31; 71,54</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-23,88; 8,91</t>
+          <t>-24,36; 10,03</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>7,82; 48,99</t>
+          <t>7,85; 49,07</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 40,85</t>
+          <t>9,39; 46,63</t>
         </is>
       </c>
     </row>
